--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>393.94</v>
+        <v>375.62</v>
       </c>
       <c r="C207" t="n">
         <v>382.75</v>
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>399.1</v>
+        <v>375.62</v>
       </c>
       <c r="C208" t="n">
         <v>383.9</v>
@@ -4184,12 +4184,30 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>399.1</v>
+        <v>375.62</v>
       </c>
       <c r="C209" t="n">
         <v>390.36</v>
       </c>
       <c r="D209" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>371.15</v>
+      </c>
+      <c r="C210" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="D210" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -4206,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6939,6 +6957,16 @@
       </c>
       <c r="B273" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -7107,28 +7135,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9382576009488975</v>
+        <v>-1.005387184021767</v>
       </c>
       <c r="J2" t="n">
+        <v>209</v>
+      </c>
+      <c r="K2" t="n">
         <v>208</v>
       </c>
-      <c r="K2" t="n">
-        <v>207</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1064902059981714</v>
+        <v>0.1216858185059602</v>
       </c>
       <c r="M2" t="n">
-        <v>18.23221406403843</v>
+        <v>18.08370654029921</v>
       </c>
       <c r="N2" t="n">
-        <v>454.3028572985751</v>
+        <v>451.0147196524173</v>
       </c>
       <c r="O2" t="n">
-        <v>21.3143814664788</v>
+        <v>21.23710713944857</v>
       </c>
       <c r="P2" t="n">
-        <v>408.7020600621958</v>
+        <v>409.3356981362624</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7185,28 +7213,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1379424156148234</v>
+        <v>0.1407083480585189</v>
       </c>
       <c r="J3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05589167854779897</v>
+        <v>0.05843100387525191</v>
       </c>
       <c r="M3" t="n">
-        <v>3.488955405642383</v>
+        <v>3.486269064230267</v>
       </c>
       <c r="N3" t="n">
-        <v>20.0191553111745</v>
+        <v>19.97177510722592</v>
       </c>
       <c r="O3" t="n">
-        <v>4.474277071346219</v>
+        <v>4.468979201923625</v>
       </c>
       <c r="P3" t="n">
-        <v>381.2350519277584</v>
+        <v>381.2089839815548</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7244,7 +7272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D209"/>
+  <dimension ref="A1:D210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11783,7 +11811,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>-34.722886395322455,173.09190425989883</t>
+          <t>-34.722933498429065,173.09171247392825</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11805,7 +11833,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>-34.72287312823574,173.09195827817865</t>
+          <t>-34.722933498429065,173.09171247392825</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11827,7 +11855,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>-34.72287312823574,173.09195827817865</t>
+          <t>-34.722933498429065,173.09171247392825</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11836,6 +11864,28 @@
         </is>
       </c>
       <c r="D209" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>-34.72294499133556,173.09166567895582</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>-34.723609231162335,173.0920987136684</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -4224,7 +4224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B274"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6967,6 +6967,16 @@
       </c>
       <c r="B274" t="n">
         <v>0.45</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D210"/>
+  <dimension ref="A1:D212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4208,6 +4208,42 @@
         <v>388.06</v>
       </c>
       <c r="D210" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="C211" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>381.44</v>
+      </c>
+      <c r="C212" t="n">
+        <v>385.74</v>
+      </c>
+      <c r="D212" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -4224,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6977,6 +7013,26 @@
       </c>
       <c r="B275" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -7145,28 +7201,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.005387184021767</v>
+        <v>-1.006978591604715</v>
       </c>
       <c r="J2" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K2" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1216858185059602</v>
+        <v>0.1241403633415776</v>
       </c>
       <c r="M2" t="n">
-        <v>18.08370654029921</v>
+        <v>17.91883940203945</v>
       </c>
       <c r="N2" t="n">
-        <v>451.0147196524173</v>
+        <v>446.7290923326244</v>
       </c>
       <c r="O2" t="n">
-        <v>21.23710713944857</v>
+        <v>21.13596679436795</v>
       </c>
       <c r="P2" t="n">
-        <v>409.3356981362624</v>
+        <v>409.3509624524347</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7223,28 +7279,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1407083480585189</v>
+        <v>0.1433356215424728</v>
       </c>
       <c r="J3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05843100387525191</v>
+        <v>0.06154058138519669</v>
       </c>
       <c r="M3" t="n">
-        <v>3.486269064230267</v>
+        <v>3.466270478579605</v>
       </c>
       <c r="N3" t="n">
-        <v>19.97177510722592</v>
+        <v>19.80975039546142</v>
       </c>
       <c r="O3" t="n">
-        <v>4.468979201923625</v>
+        <v>4.450814576620938</v>
       </c>
       <c r="P3" t="n">
-        <v>381.2089839815548</v>
+        <v>381.1840759292105</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7282,7 +7338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D210"/>
+  <dimension ref="A1:D212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11901,6 +11957,50 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-34.72291624617998,173.0917827187059</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-34.72361141663722,173.09208981523204</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-34.7229185344836,173.091773401591</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-34.72361519622168,173.09207442617046</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4246,6 +4246,42 @@
       <c r="D212" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="C213" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="C214" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B277"/>
+  <dimension ref="A1:B279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7033,6 +7069,26 @@
       </c>
       <c r="B277" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -7201,28 +7257,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.006978591604715</v>
+        <v>-1.007175067018431</v>
       </c>
       <c r="J2" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K2" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1241403633415776</v>
+        <v>0.1263152841488683</v>
       </c>
       <c r="M2" t="n">
-        <v>17.91883940203945</v>
+        <v>17.75715733338517</v>
       </c>
       <c r="N2" t="n">
-        <v>446.7290923326244</v>
+        <v>442.5208083706686</v>
       </c>
       <c r="O2" t="n">
-        <v>21.13596679436795</v>
+        <v>21.03617855910785</v>
       </c>
       <c r="P2" t="n">
-        <v>409.3509624524347</v>
+        <v>409.3528851726008</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7279,28 +7335,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1433356215424728</v>
+        <v>0.1379291016063612</v>
       </c>
       <c r="J3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06154058138519669</v>
+        <v>0.05798852310539349</v>
       </c>
       <c r="M3" t="n">
-        <v>3.466270478579605</v>
+        <v>3.466498717058681</v>
       </c>
       <c r="N3" t="n">
-        <v>19.80975039546142</v>
+        <v>19.73630288582791</v>
       </c>
       <c r="O3" t="n">
-        <v>4.450814576620938</v>
+        <v>4.442555895633494</v>
       </c>
       <c r="P3" t="n">
-        <v>381.1840759292105</v>
+        <v>381.2358451104824</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7338,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D212"/>
+  <dimension ref="A1:D214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12001,6 +12057,50 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>-34.72291367505146,173.09179318737367</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>-34.72362193261909,173.0920469980436</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-34.72291796883558,173.0917757046981</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-34.72362892612436,173.09201852303693</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4280,6 +4280,42 @@
         <v>380.4</v>
       </c>
       <c r="D214" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="C215" t="n">
+        <v>381.02</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="C216" t="n">
+        <v>380.03</v>
+      </c>
+      <c r="D216" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -4296,7 +4332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B279"/>
+  <dimension ref="A1:B281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7089,6 +7125,26 @@
       </c>
       <c r="B279" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -7257,28 +7313,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.007175067018431</v>
+        <v>-1.005606645617511</v>
       </c>
       <c r="J2" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1263152841488683</v>
+        <v>0.1280810924209291</v>
       </c>
       <c r="M2" t="n">
-        <v>17.75715733338517</v>
+        <v>17.60120261306372</v>
       </c>
       <c r="N2" t="n">
-        <v>442.5208083706686</v>
+        <v>438.3932575153871</v>
       </c>
       <c r="O2" t="n">
-        <v>21.03617855910785</v>
+        <v>20.93784271398052</v>
       </c>
       <c r="P2" t="n">
-        <v>409.3528851726008</v>
+        <v>409.3376431972178</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7335,28 +7391,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1379291016063612</v>
+        <v>0.1307359181425005</v>
       </c>
       <c r="J3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05798852310539349</v>
+        <v>0.05290372156471101</v>
       </c>
       <c r="M3" t="n">
-        <v>3.466498717058681</v>
+        <v>3.478150933949156</v>
       </c>
       <c r="N3" t="n">
-        <v>19.73630288582791</v>
+        <v>19.72925534974211</v>
       </c>
       <c r="O3" t="n">
-        <v>4.442555895633494</v>
+        <v>4.441762639959739</v>
       </c>
       <c r="P3" t="n">
-        <v>381.2358451104824</v>
+        <v>381.3049951290953</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7394,7 +7450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12101,6 +12157,50 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-34.72291334080469,173.09179454830044</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-34.72362733201713,173.09202501366389</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-34.72291334080469,173.09179454830044</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-34.723629877446264,173.09201464959816</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D216"/>
+  <dimension ref="A1:D218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4318,6 +4318,42 @@
       <c r="D216" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>378.95</v>
+      </c>
+      <c r="C217" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>375.24</v>
+      </c>
+      <c r="C218" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7145,6 +7181,26 @@
       </c>
       <c r="B281" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -7313,28 +7369,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.005606645617511</v>
+        <v>-1.014318510943319</v>
       </c>
       <c r="J2" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1280810924209291</v>
+        <v>0.1320607239443358</v>
       </c>
       <c r="M2" t="n">
-        <v>17.60120261306372</v>
+        <v>17.48032012853536</v>
       </c>
       <c r="N2" t="n">
-        <v>438.3932575153871</v>
+        <v>434.6248581096964</v>
       </c>
       <c r="O2" t="n">
-        <v>20.93784271398052</v>
+        <v>20.8476583363623</v>
       </c>
       <c r="P2" t="n">
-        <v>409.3376431972178</v>
+        <v>409.4226652645464</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7391,28 +7447,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1307359181425005</v>
+        <v>0.1217624958182433</v>
       </c>
       <c r="J3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05290372156471101</v>
+        <v>0.04640258724036983</v>
       </c>
       <c r="M3" t="n">
-        <v>3.478150933949156</v>
+        <v>3.501225628104355</v>
       </c>
       <c r="N3" t="n">
-        <v>19.72925534974211</v>
+        <v>19.82801816119085</v>
       </c>
       <c r="O3" t="n">
-        <v>4.441762639959739</v>
+        <v>4.452866286021943</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3049951290953</v>
+        <v>381.3915857911695</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7450,7 +7506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D216"/>
+  <dimension ref="A1:D218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12201,6 +12257,50 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-34.72292493658771,173.09174733460398</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-34.723631754378296,173.0920070074079</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>-34.722934475455375,173.09170849583265</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>-34.72363224289477,173.0920050183446</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0013/nzd0013.xlsx
+++ b/data/nzd0013/nzd0013.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D218"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4354,6 +4354,24 @@
       <c r="D218" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="C219" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7201,6 +7219,16 @@
       </c>
       <c r="B283" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -7369,28 +7397,28 @@
         <v>0.0434</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.014318510943319</v>
+        <v>-1.018780971014785</v>
       </c>
       <c r="J2" t="n">
+        <v>218</v>
+      </c>
+      <c r="K2" t="n">
         <v>217</v>
       </c>
-      <c r="K2" t="n">
-        <v>216</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1320607239443358</v>
+        <v>0.1340956762536684</v>
       </c>
       <c r="M2" t="n">
-        <v>17.48032012853536</v>
+        <v>17.42108087677977</v>
       </c>
       <c r="N2" t="n">
-        <v>434.6248581096964</v>
+        <v>432.7613802846287</v>
       </c>
       <c r="O2" t="n">
-        <v>20.8476583363623</v>
+        <v>20.80291759068013</v>
       </c>
       <c r="P2" t="n">
-        <v>409.4226652645464</v>
+        <v>409.4663958494185</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -7447,28 +7475,28 @@
         <v>0.0697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1217624958182433</v>
+        <v>0.1192031420387581</v>
       </c>
       <c r="J3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04640258724036983</v>
+        <v>0.04484798414828128</v>
       </c>
       <c r="M3" t="n">
-        <v>3.501225628104355</v>
+        <v>3.500695474646783</v>
       </c>
       <c r="N3" t="n">
-        <v>19.82801816119085</v>
+        <v>19.78369613543935</v>
       </c>
       <c r="O3" t="n">
-        <v>4.452866286021943</v>
+        <v>4.447886704429346</v>
       </c>
       <c r="P3" t="n">
-        <v>381.3915857911695</v>
+        <v>381.4163951084471</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -7506,7 +7534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D218"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12301,6 +12329,28 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-34.72293074732798,173.09172367540742</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>-34.72362622642641,173.09202951522758</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
